--- a/Data/Excel/skill.xlsx
+++ b/Data/Excel/skill.xlsx
@@ -144,7 +144,7 @@
     <t>Single target magical damage</t>
   </si>
   <si>
-    <t>Icon/Skill/fireball</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_fireball_icon.png</t>
   </si>
   <si>
     <t>Frost Nova</t>
@@ -153,7 +153,7 @@
     <t>Area damage and slow at target point</t>
   </si>
   <si>
-    <t>Icon/Skill/frost_nova</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_freeze_icon.png</t>
   </si>
   <si>
     <t>Ice Tower Shot</t>
@@ -162,7 +162,7 @@
     <t>Tower hit applies damage and freeze slow</t>
   </si>
   <si>
-    <t>Icon/Skill/ice_shot</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_freeze_icon.png</t>
   </si>
   <si>
     <t>Heal</t>
@@ -171,7 +171,7 @@
     <t>Single target friendly heal</t>
   </si>
   <si>
-    <t>Icon/Skill/heal</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_bomb_icon.png</t>
   </si>
   <si>
     <t>Poison Cloud</t>
@@ -180,7 +180,7 @@
     <t>Apply poison damage over time in area</t>
   </si>
   <si>
-    <t>Icon/Skill/poison_cloud</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_bomb_icon.png</t>
   </si>
   <si>
     <t>Stun Bolt</t>
@@ -189,7 +189,7 @@
     <t>Single target damage and stun</t>
   </si>
   <si>
-    <t>Icon/Skill/stun_bolt</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_lightning_icon.png</t>
   </si>
   <si>
     <t>Attack Speed Aura</t>
@@ -198,7 +198,7 @@
     <t>Passive attack speed aura placeholder</t>
   </si>
   <si>
-    <t>Icon/Skill/aura_attack_speed</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Skills/ui_td_skill_lightning_icon.png</t>
   </si>
 </sst>
 </file>

--- a/Data/Excel/skill.xlsx
+++ b/Data/Excel/skill.xlsx
@@ -691,7 +691,7 @@
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="B5" s="5">
-        <v>1001</v>
+        <v>50000001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>37</v>
@@ -724,13 +724,13 @@
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="N5" s="2">
         <v>20</v>
       </c>
       <c r="O5" s="2">
-        <v>1001</v>
+        <v>50200001</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="B6" s="5">
-        <v>1002</v>
+        <v>50000002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>40</v>
@@ -774,13 +774,13 @@
         <v>8</v>
       </c>
       <c r="M6" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="N6" s="2">
         <v>40</v>
       </c>
       <c r="O6" s="2">
-        <v>1002</v>
+        <v>50200002</v>
       </c>
       <c r="P6" s="2">
         <v>0</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="B7" s="5">
-        <v>1003</v>
+        <v>50000003</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>43</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="2">
-        <v>1003</v>
+        <v>50200003</v>
       </c>
       <c r="P7" s="2">
         <v>0</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1">
       <c r="B8" s="5">
-        <v>1004</v>
+        <v>50000004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>46</v>
@@ -874,13 +874,13 @@
         <v>5</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="N8" s="2">
         <v>25</v>
       </c>
       <c r="O8" s="2">
-        <v>1004</v>
+        <v>50200004</v>
       </c>
       <c r="P8" s="2">
         <v>0</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="B9" s="5">
-        <v>1005</v>
+        <v>50000005</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>49</v>
@@ -924,13 +924,13 @@
         <v>10</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="N9" s="2">
         <v>50</v>
       </c>
       <c r="O9" s="2">
-        <v>1005</v>
+        <v>50200005</v>
       </c>
       <c r="P9" s="2">
         <v>0</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
       <c r="B10" s="5">
-        <v>1006</v>
+        <v>50000006</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>52</v>
@@ -974,13 +974,13 @@
         <v>6</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="N10" s="2">
         <v>35</v>
       </c>
       <c r="O10" s="2">
-        <v>1006</v>
+        <v>50200006</v>
       </c>
       <c r="P10" s="2">
         <v>0</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
       <c r="B11" s="5">
-        <v>2001</v>
+        <v>50001001</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>55</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2">
-        <v>3003</v>
+        <v>50500003</v>
       </c>
       <c r="Q11" s="3" t="b">
         <v>1</v>
